--- a/Identifying Improvement-Related Concerns in Comments with LLMs (RQ1)/Gemini.xlsx
+++ b/Identifying Improvement-Related Concerns in Comments with LLMs (RQ1)/Gemini.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\MSR_AUTOCOMBAT\Capturing Improvement-Related Concerns (RQ1)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suborno\Downloads\AUTOCOMBAT Dataset\Identifying Improvement-Related Concerns in Comments with LLMs (RQ1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69E9F15-B262-4E5D-8091-7ED1D8721077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95591C4-86C7-408F-A89A-78DD059BE361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="2131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3278" uniqueCount="2157">
   <si>
     <t>answer_id</t>
   </si>
@@ -13393,6 +13393,84 @@
   <si>
     <t>Thanks man! The problem is solved! Your solution engages me more to find solution from bugs more! - GC</t>
   </si>
+  <si>
+    <t>The labelled comment mainly shares an external reference, example, demo, documentation, or related resource; Gemini turned that supporting material into a required answer change.</t>
+  </si>
+  <si>
+    <t>External reference</t>
+  </si>
+  <si>
+    <t>Gemini missed an IA comment asking for clarification, explanatory context, examples, documentation, or missing rationale.</t>
+  </si>
+  <si>
+    <t>Explanatory request</t>
+  </si>
+  <si>
+    <t>The labelled comment describes a local environment, personal setup, or user-specific symptom; Gemini generalized it into an answer-wide improvement.</t>
+  </si>
+  <si>
+    <t>User-specific context</t>
+  </si>
+  <si>
+    <t>The labelled comment is mainly acknowledgement, praise, confirmation, or resolution feedback; Gemini incorrectly treated it as an improvement request.</t>
+  </si>
+  <si>
+    <t>Appreciation resolution</t>
+  </si>
+  <si>
+    <t>Gemini missed an IA comment that reports incorrect behavior, a failing case, unsafe logic, a typo, or another necessary correctness fix.</t>
+  </si>
+  <si>
+    <t>Correctness issue</t>
+  </si>
+  <si>
+    <t>Gemini missed an IA comment about an API, dependency, library, framework, language feature, browser/runtime behavior, or environment-specific update.</t>
+  </si>
+  <si>
+    <t>Version/API update</t>
+  </si>
+  <si>
+    <t>Gemini missed an IA comment whose improvement signal is brief, indirect, or weakly stated rather than phrased as an explicit request.</t>
+  </si>
+  <si>
+    <t>Implicit concern</t>
+  </si>
+  <si>
+    <t>The labelled comment provides an optional technical note, alternative, edge case, or side detail; Gemini treated this supplementary information as a required edit.</t>
+  </si>
+  <si>
+    <t>Supplementary note</t>
+  </si>
+  <si>
+    <t>The labelled comment is a follow-up question or discussion prompt without a concrete addressed edit; Gemini treated it as actionable.</t>
+  </si>
+  <si>
+    <t>Clarification follow-up</t>
+  </si>
+  <si>
+    <t>Gemini missed an IA comment that requests or implies a performance, complexity, memory, or optimization improvement.</t>
+  </si>
+  <si>
+    <t>Performance concern</t>
+  </si>
+  <si>
+    <t>The labelled comment is opinion-oriented, meta-level, or conversational, but Gemini interpreted it as a required technical correction.</t>
+  </si>
+  <si>
+    <t>Meta discussion</t>
+  </si>
+  <si>
+    <t>Gemini missed an IA comment embedded in a longer thread with surrounding general discussion, where the actionable signal was diluted by noise.</t>
+  </si>
+  <si>
+    <t>Mixed thread concern</t>
+  </si>
+  <si>
+    <t>Comment_misclassification_category</t>
+  </si>
+  <si>
+    <t>Comment_misclassification_reason</t>
+  </si>
 </sst>
 </file>
 
@@ -13435,7 +13513,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -13471,11 +13549,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -13487,6 +13578,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13791,7 +13888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J791"/>
+  <dimension ref="A1:L791"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -13799,9 +13896,11 @@
     <col min="3" max="3" width="16.109375" customWidth="1"/>
     <col min="4" max="4" width="36.77734375" customWidth="1"/>
     <col min="5" max="5" width="44" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="27" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -13829,11 +13928,17 @@
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="6" t="s">
+        <v>2155</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>6496</v>
       </c>
@@ -13864,8 +13969,14 @@
       <c r="J2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K2" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>9788</v>
       </c>
@@ -13897,7 +14008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>21311</v>
       </c>
@@ -13927,7 +14038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>30287</v>
       </c>
@@ -13957,7 +14068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>70545</v>
       </c>
@@ -13986,8 +14097,14 @@
       <c r="J6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>85342</v>
       </c>
@@ -14019,7 +14136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>95259</v>
       </c>
@@ -14050,8 +14167,14 @@
       <c r="J8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>110337</v>
       </c>
@@ -14081,7 +14204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>120716</v>
       </c>
@@ -14113,7 +14236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>126570</v>
       </c>
@@ -14144,8 +14267,14 @@
       <c r="J11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>140725</v>
       </c>
@@ -14175,7 +14304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>141100</v>
       </c>
@@ -14205,7 +14334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>142483</v>
       </c>
@@ -14237,7 +14366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>159786</v>
       </c>
@@ -14269,7 +14398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>164750</v>
       </c>
@@ -14299,7 +14428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>164934</v>
       </c>
@@ -14331,7 +14460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>176039</v>
       </c>
@@ -14360,8 +14489,14 @@
       <c r="J18" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>185146</v>
       </c>
@@ -14391,7 +14526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>194414</v>
       </c>
@@ -14421,7 +14556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>204882</v>
       </c>
@@ -14453,7 +14588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>209899</v>
       </c>
@@ -14485,7 +14620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>220565</v>
       </c>
@@ -14517,7 +14652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>223320</v>
       </c>
@@ -14549,7 +14684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>226036</v>
       </c>
@@ -14581,7 +14716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>241975</v>
       </c>
@@ -14613,7 +14748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>244547</v>
       </c>
@@ -14645,7 +14780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>277047</v>
       </c>
@@ -14677,7 +14812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>279014</v>
       </c>
@@ -14706,8 +14841,14 @@
       <c r="J29" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>281280</v>
       </c>
@@ -14736,8 +14877,14 @@
       <c r="J30" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>298208</v>
       </c>
@@ -14769,7 +14916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>298852</v>
       </c>
@@ -14801,7 +14948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>301581</v>
       </c>
@@ -14832,8 +14979,14 @@
       <c r="J33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>310625</v>
       </c>
@@ -14863,7 +15016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>319953</v>
       </c>
@@ -14895,7 +15048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>326469</v>
       </c>
@@ -14924,8 +15077,14 @@
       <c r="J36" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K36" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>332765</v>
       </c>
@@ -14955,7 +15114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>335936</v>
       </c>
@@ -14985,7 +15144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>336913</v>
       </c>
@@ -15015,7 +15174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>343774</v>
       </c>
@@ -15047,7 +15206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>347906</v>
       </c>
@@ -15077,7 +15236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>352488</v>
       </c>
@@ -15107,7 +15266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>357449</v>
       </c>
@@ -15139,7 +15298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>358705</v>
       </c>
@@ -15171,7 +15330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>360963</v>
       </c>
@@ -15201,7 +15360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>361483</v>
       </c>
@@ -15233,7 +15392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>369009</v>
       </c>
@@ -15263,7 +15422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>397997</v>
       </c>
@@ -15295,7 +15454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>467919</v>
       </c>
@@ -15327,7 +15486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>472622</v>
       </c>
@@ -15359,7 +15518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>473009</v>
       </c>
@@ -15391,7 +15550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>477308</v>
       </c>
@@ -15423,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>479795</v>
       </c>
@@ -15453,7 +15612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>489465</v>
       </c>
@@ -15483,7 +15642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>494878</v>
       </c>
@@ -15513,7 +15672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>521708</v>
       </c>
@@ -15542,8 +15701,14 @@
       <c r="J56" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K56" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>538909</v>
       </c>
@@ -15575,7 +15740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>548083</v>
       </c>
@@ -15605,7 +15770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>572011</v>
       </c>
@@ -15635,7 +15800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>574360</v>
       </c>
@@ -15665,7 +15830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>580048</v>
       </c>
@@ -15697,7 +15862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>599914</v>
       </c>
@@ -15727,7 +15892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>600719</v>
       </c>
@@ -15757,7 +15922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>619262</v>
       </c>
@@ -15788,8 +15953,14 @@
       <c r="J64" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K64" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>703985</v>
       </c>
@@ -15821,7 +15992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>765976</v>
       </c>
@@ -15853,7 +16024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>817430</v>
       </c>
@@ -15885,7 +16056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>888576</v>
       </c>
@@ -15917,7 +16088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>890877</v>
       </c>
@@ -15947,7 +16118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>906529</v>
       </c>
@@ -15979,7 +16150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>908443</v>
       </c>
@@ -16011,7 +16182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>981624</v>
       </c>
@@ -16043,7 +16214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>983942</v>
       </c>
@@ -16074,8 +16245,14 @@
       <c r="J73" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K73" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>1025435</v>
       </c>
@@ -16107,7 +16284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>1068851</v>
       </c>
@@ -16136,8 +16313,14 @@
       <c r="J75" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K75" s="1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>1139981</v>
       </c>
@@ -16169,7 +16352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>1144418</v>
       </c>
@@ -16201,7 +16384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>1165320</v>
       </c>
@@ -16231,7 +16414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>1230699</v>
       </c>
@@ -16263,7 +16446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>1253939</v>
       </c>
@@ -16294,8 +16477,14 @@
       <c r="J80" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K80" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>1270500</v>
       </c>
@@ -16325,7 +16514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>1293673</v>
       </c>
@@ -16357,7 +16546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>2561008</v>
       </c>
@@ -16388,8 +16577,14 @@
       <c r="J83" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K83" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>3295972</v>
       </c>
@@ -16419,7 +16614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>4295743</v>
       </c>
@@ -16450,8 +16645,14 @@
       <c r="J85" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K85" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>6260097</v>
       </c>
@@ -16482,8 +16683,14 @@
       <c r="J86" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K86" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>6468505</v>
       </c>
@@ -16515,7 +16722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>7604717</v>
       </c>
@@ -16547,7 +16754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>8244949</v>
       </c>
@@ -16577,7 +16784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>8609238</v>
       </c>
@@ -16609,7 +16816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>8909233</v>
       </c>
@@ -16640,8 +16847,14 @@
       <c r="J91" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K91" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>10149358</v>
       </c>
@@ -16673,7 +16886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>11475779</v>
       </c>
@@ -16705,7 +16918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>11497391</v>
       </c>
@@ -16737,7 +16950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>12739974</v>
       </c>
@@ -16768,8 +16981,14 @@
       <c r="J95" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K95" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>14390676</v>
       </c>
@@ -16799,7 +17018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>15179418</v>
       </c>
@@ -16830,8 +17049,14 @@
       <c r="J97" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K97" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>20612691</v>
       </c>
@@ -16863,7 +17088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>23051095</v>
       </c>
@@ -16893,7 +17118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>23996414</v>
       </c>
@@ -16923,7 +17148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>25802742</v>
       </c>
@@ -16953,7 +17178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>37103131</v>
       </c>
@@ -16983,7 +17208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>37262973</v>
       </c>
@@ -17012,8 +17237,14 @@
       <c r="J103" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K103" s="1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>40914267</v>
       </c>
@@ -17045,7 +17276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46046703</v>
       </c>
@@ -17077,7 +17308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>51031070</v>
       </c>
@@ -17107,7 +17338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>51953411</v>
       </c>
@@ -17136,8 +17367,14 @@
       <c r="J107" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K107" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>507069</v>
       </c>
@@ -17169,7 +17406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>754910</v>
       </c>
@@ -17199,7 +17436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>48709142</v>
       </c>
@@ -17231,7 +17468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>241155</v>
       </c>
@@ -17263,7 +17500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>78988593</v>
       </c>
@@ -17294,8 +17531,14 @@
       <c r="J112" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K112" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>578356</v>
       </c>
@@ -17327,7 +17570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>181190</v>
       </c>
@@ -17359,7 +17602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>203517</v>
       </c>
@@ -17391,7 +17634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>79417516</v>
       </c>
@@ -17421,7 +17664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>79438279</v>
       </c>
@@ -17453,7 +17696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>79286372</v>
       </c>
@@ -17485,7 +17728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>48259</v>
       </c>
@@ -17517,7 +17760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>280132</v>
       </c>
@@ -17549,7 +17792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>79165236</v>
       </c>
@@ -17579,7 +17822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>482587</v>
       </c>
@@ -17611,7 +17854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>79469718</v>
       </c>
@@ -17641,7 +17884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="216" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>55553392</v>
       </c>
@@ -17672,8 +17915,14 @@
       <c r="J124" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K124" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>274234</v>
       </c>
@@ -17703,7 +17952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>79089213</v>
       </c>
@@ -17735,7 +17984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>79092862</v>
       </c>
@@ -17767,7 +18016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>479795</v>
       </c>
@@ -17797,7 +18046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>890848</v>
       </c>
@@ -17827,7 +18076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>339505</v>
       </c>
@@ -17859,7 +18108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>254233</v>
       </c>
@@ -17889,7 +18138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>441553</v>
       </c>
@@ -17920,8 +18169,14 @@
       <c r="J132" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K132" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>995822</v>
       </c>
@@ -17953,7 +18208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>260877</v>
       </c>
@@ -17985,7 +18240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>1276813</v>
       </c>
@@ -18017,7 +18272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>79217556</v>
       </c>
@@ -18049,7 +18304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>1052789</v>
       </c>
@@ -18081,7 +18336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>1115242</v>
       </c>
@@ -18112,8 +18367,14 @@
       <c r="J138" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K138" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>507608</v>
       </c>
@@ -18143,7 +18404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>255095</v>
       </c>
@@ -18175,7 +18436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>248369</v>
       </c>
@@ -18205,7 +18466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>79167904</v>
       </c>
@@ -18237,7 +18498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>210859</v>
       </c>
@@ -18267,7 +18528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>309448</v>
       </c>
@@ -18297,7 +18558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>330546</v>
       </c>
@@ -18326,8 +18587,14 @@
       <c r="J145" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K145" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>42323184</v>
       </c>
@@ -18359,7 +18626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>80194</v>
       </c>
@@ -18388,8 +18655,14 @@
       <c r="J147" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K147" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>79301080</v>
       </c>
@@ -18419,7 +18692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>96722</v>
       </c>
@@ -18451,7 +18724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>79168741</v>
       </c>
@@ -18483,7 +18756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>79497372</v>
       </c>
@@ -18515,7 +18788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>79479669</v>
       </c>
@@ -18544,8 +18817,14 @@
       <c r="J152" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K152" s="1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>621202</v>
       </c>
@@ -18575,7 +18854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>79226523</v>
       </c>
@@ -18607,7 +18886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>553178</v>
       </c>
@@ -18638,8 +18917,14 @@
       <c r="J155" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K155" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>79106007</v>
       </c>
@@ -18669,7 +18954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>78969431</v>
       </c>
@@ -18701,7 +18986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>300510</v>
       </c>
@@ -18733,7 +19018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>172011</v>
       </c>
@@ -18764,8 +19049,14 @@
       <c r="J159" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K159" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>244256</v>
       </c>
@@ -18797,7 +19088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>575346</v>
       </c>
@@ -18829,7 +19120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>79448627</v>
       </c>
@@ -18861,7 +19152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>229957</v>
       </c>
@@ -18890,8 +19181,14 @@
       <c r="J163" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K163" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>491272</v>
       </c>
@@ -18923,7 +19220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>172845</v>
       </c>
@@ -18955,7 +19252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>79149501</v>
       </c>
@@ -18985,7 +19282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>79341665</v>
       </c>
@@ -19016,8 +19313,14 @@
       <c r="J167" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K167" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L167" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>265409</v>
       </c>
@@ -19049,7 +19352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>79347305</v>
       </c>
@@ -19080,8 +19383,14 @@
       <c r="J169" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K169" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L169" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>78958806</v>
       </c>
@@ -19111,7 +19420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>79088080</v>
       </c>
@@ -19143,7 +19452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>478433</v>
       </c>
@@ -19174,8 +19483,14 @@
       <c r="J172" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K172" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L172" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>78989175</v>
       </c>
@@ -19207,7 +19522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>79337931</v>
       </c>
@@ -19237,7 +19552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>79079876</v>
       </c>
@@ -19269,7 +19584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>79148316</v>
       </c>
@@ -19301,7 +19616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>452072</v>
       </c>
@@ -19333,7 +19648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>79263313</v>
       </c>
@@ -19365,7 +19680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>498226</v>
       </c>
@@ -19395,7 +19710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>79117670</v>
       </c>
@@ -19427,7 +19742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>79352585</v>
       </c>
@@ -19459,7 +19774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>79225523</v>
       </c>
@@ -19489,7 +19804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>239715</v>
       </c>
@@ -19521,7 +19836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>38387640</v>
       </c>
@@ -19553,7 +19868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>759420</v>
       </c>
@@ -19585,7 +19900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>52472732</v>
       </c>
@@ -19617,7 +19932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>843725</v>
       </c>
@@ -19647,7 +19962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>307203</v>
       </c>
@@ -19679,7 +19994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>135982</v>
       </c>
@@ -19708,8 +20023,14 @@
       <c r="J189" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K189" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L189" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>21724</v>
       </c>
@@ -19741,7 +20062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>79023736</v>
       </c>
@@ -19773,7 +20094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>169490</v>
       </c>
@@ -19805,7 +20126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>18695700</v>
       </c>
@@ -19836,8 +20157,14 @@
       <c r="J193" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K193" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L193" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>244299</v>
       </c>
@@ -19869,7 +20196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>563838</v>
       </c>
@@ -19900,8 +20227,14 @@
       <c r="J195" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K195" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L195" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>384709</v>
       </c>
@@ -19933,7 +20266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>78949385</v>
       </c>
@@ -19965,7 +20298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>1004960</v>
       </c>
@@ -19997,7 +20330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>587502</v>
       </c>
@@ -20029,7 +20362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>79322689</v>
       </c>
@@ -20061,7 +20394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>33328657</v>
       </c>
@@ -20092,8 +20425,14 @@
       <c r="J201" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K201" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L201" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>57897625</v>
       </c>
@@ -20123,7 +20462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>79160348</v>
       </c>
@@ -20155,7 +20494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>79013367</v>
       </c>
@@ -20187,7 +20526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>79199279</v>
       </c>
@@ -20217,7 +20556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>79380087</v>
       </c>
@@ -20247,7 +20586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>1098076</v>
       </c>
@@ -20279,7 +20618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>7643</v>
       </c>
@@ -20309,7 +20648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>10103</v>
       </c>
@@ -20341,7 +20680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>57807</v>
       </c>
@@ -20373,7 +20712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>59727</v>
       </c>
@@ -20403,7 +20742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>73819</v>
       </c>
@@ -20435,7 +20774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>75502</v>
       </c>
@@ -20467,7 +20806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>86341</v>
       </c>
@@ -20499,7 +20838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>139626</v>
       </c>
@@ -20531,7 +20870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>141216</v>
       </c>
@@ -20561,7 +20900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>146472</v>
       </c>
@@ -20593,7 +20932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>159559</v>
       </c>
@@ -20624,8 +20963,14 @@
       <c r="J218" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K218" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L218" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>178092</v>
       </c>
@@ -20657,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>189558</v>
       </c>
@@ -20688,8 +21033,14 @@
       <c r="J220" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K220" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L220" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>209931</v>
       </c>
@@ -20721,7 +21072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>224675</v>
       </c>
@@ -20753,7 +21104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>228983</v>
       </c>
@@ -20785,7 +21136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>237084</v>
       </c>
@@ -20817,7 +21168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>240315</v>
       </c>
@@ -20849,7 +21200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>287661</v>
       </c>
@@ -20880,8 +21231,14 @@
       <c r="J226" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K226" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L226" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>300831</v>
       </c>
@@ -20913,7 +21270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>337846</v>
       </c>
@@ -20943,7 +21300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>381771</v>
       </c>
@@ -20975,7 +21332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>388753</v>
       </c>
@@ -21004,8 +21361,14 @@
       <c r="J230" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K230" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L230" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>389734</v>
       </c>
@@ -21035,7 +21398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>475873</v>
       </c>
@@ -21065,7 +21428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>484086</v>
       </c>
@@ -21097,7 +21460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>505326</v>
       </c>
@@ -21127,7 +21490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>510907</v>
       </c>
@@ -21159,7 +21522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>520556</v>
       </c>
@@ -21191,7 +21554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>550997</v>
       </c>
@@ -21223,7 +21586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>846598</v>
       </c>
@@ -21255,7 +21618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>934008</v>
       </c>
@@ -21287,7 +21650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>1045147</v>
       </c>
@@ -21319,7 +21682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>1057065</v>
       </c>
@@ -21351,7 +21714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>1100653</v>
       </c>
@@ -21383,7 +21746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>1309268</v>
       </c>
@@ -21415,7 +21778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>1319353</v>
       </c>
@@ -21445,7 +21808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>1781590</v>
       </c>
@@ -21477,7 +21840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>2264722</v>
       </c>
@@ -21507,7 +21870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>2755273</v>
       </c>
@@ -21537,7 +21900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>3392370</v>
       </c>
@@ -21569,7 +21932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>3673447</v>
       </c>
@@ -21601,7 +21964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>5337329</v>
       </c>
@@ -21633,7 +21996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>6663292</v>
       </c>
@@ -21663,7 +22026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>8385658</v>
       </c>
@@ -21693,7 +22056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>9058322</v>
       </c>
@@ -21725,7 +22088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>10344231</v>
       </c>
@@ -21756,8 +22119,14 @@
       <c r="J254" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K254" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L254" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>11784778</v>
       </c>
@@ -21787,7 +22156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>12141207</v>
       </c>
@@ -21816,8 +22185,14 @@
       <c r="J256" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K256" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="L256" s="1" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>12214880</v>
       </c>
@@ -21847,7 +22222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>13562327</v>
       </c>
@@ -21879,7 +22254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>13633860</v>
       </c>
@@ -21908,8 +22283,14 @@
       <c r="J259" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K259" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L259" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>13869233</v>
       </c>
@@ -21940,8 +22321,14 @@
       <c r="J260" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K260" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L260" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>14487936</v>
       </c>
@@ -21973,7 +22360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>17558764</v>
       </c>
@@ -22005,7 +22392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>24085681</v>
       </c>
@@ -22034,8 +22421,14 @@
       <c r="J263" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="264" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K263" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L263" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>32101507</v>
       </c>
@@ -22065,7 +22458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>33558141</v>
       </c>
@@ -22096,8 +22489,14 @@
       <c r="J265" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K265" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L265" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>34803630</v>
       </c>
@@ -22129,7 +22528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>38490727</v>
       </c>
@@ -22161,7 +22560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>39133654</v>
       </c>
@@ -22193,7 +22592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>40105714</v>
       </c>
@@ -22225,7 +22624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>48374171</v>
       </c>
@@ -22255,7 +22654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>54358758</v>
       </c>
@@ -22287,7 +22686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>60780210</v>
       </c>
@@ -22318,8 +22717,14 @@
       <c r="J272" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K272" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L272" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>69642922</v>
       </c>
@@ -22350,8 +22755,14 @@
       <c r="J273" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K273" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L273" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>378029</v>
       </c>
@@ -22383,7 +22794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>1318009</v>
       </c>
@@ -22415,7 +22826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>78943100</v>
       </c>
@@ -22445,7 +22856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>79028336</v>
       </c>
@@ -22477,7 +22888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>4383103</v>
       </c>
@@ -22508,8 +22919,14 @@
       <c r="J278" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K278" s="1" t="s">
+        <v>2152</v>
+      </c>
+      <c r="L278" s="1" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>112184</v>
       </c>
@@ -22541,7 +22958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>78974711</v>
       </c>
@@ -22573,7 +22990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>7191254</v>
       </c>
@@ -22605,7 +23022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>79030599</v>
       </c>
@@ -22637,7 +23054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>298276</v>
       </c>
@@ -22669,7 +23086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>79422643</v>
       </c>
@@ -22701,7 +23118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>183909</v>
       </c>
@@ -22733,7 +23150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>79059467</v>
       </c>
@@ -22765,7 +23182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>1063119</v>
       </c>
@@ -22797,7 +23214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>13993400</v>
       </c>
@@ -22827,7 +23244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>114831</v>
       </c>
@@ -22856,8 +23273,14 @@
       <c r="J289" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="290" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K289" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L289" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>136496</v>
       </c>
@@ -22889,7 +23312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>340164</v>
       </c>
@@ -22919,7 +23342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>289567</v>
       </c>
@@ -22950,8 +23373,14 @@
       <c r="J292" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K292" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L292" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>79522389</v>
       </c>
@@ -22983,7 +23412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>79142717</v>
       </c>
@@ -23012,8 +23441,14 @@
       <c r="J294" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="295" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K294" s="1" t="s">
+        <v>2154</v>
+      </c>
+      <c r="L294" s="1" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>9050384</v>
       </c>
@@ -23045,7 +23480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>28720127</v>
       </c>
@@ -23077,7 +23512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>16627277</v>
       </c>
@@ -23108,8 +23543,14 @@
       <c r="J297" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K297" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L297" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>165256</v>
       </c>
@@ -23139,7 +23580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>13957915</v>
       </c>
@@ -23171,7 +23612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>78998331</v>
       </c>
@@ -23203,7 +23644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>78936376</v>
       </c>
@@ -23235,7 +23676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>39852836</v>
       </c>
@@ -23267,7 +23708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>11789703</v>
       </c>
@@ -23299,7 +23740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>28576383</v>
       </c>
@@ -23331,7 +23772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>827312</v>
       </c>
@@ -23363,7 +23804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>768577</v>
       </c>
@@ -23392,8 +23833,14 @@
       <c r="J306" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="307" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K306" s="1" t="s">
+        <v>2154</v>
+      </c>
+      <c r="L306" s="1" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>17909525</v>
       </c>
@@ -23425,7 +23872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>79226343</v>
       </c>
@@ -23457,7 +23904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>219192</v>
       </c>
@@ -23489,7 +23936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>754523</v>
       </c>
@@ -23518,8 +23965,14 @@
       <c r="J310" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="311" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K310" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L310" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>43281595</v>
       </c>
@@ -23551,7 +24004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>175677</v>
       </c>
@@ -23581,7 +24034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>216412</v>
       </c>
@@ -23613,7 +24066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>79538834</v>
       </c>
@@ -23645,7 +24098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>17598</v>
       </c>
@@ -23677,7 +24130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>34516129</v>
       </c>
@@ -23707,7 +24160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>75867</v>
       </c>
@@ -23737,7 +24190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>173090</v>
       </c>
@@ -23769,7 +24222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>541763</v>
       </c>
@@ -23801,7 +24254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>79369408</v>
       </c>
@@ -23831,7 +24284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>79033230</v>
       </c>
@@ -23862,8 +24315,14 @@
       <c r="J321" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K321" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L321" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>322979</v>
       </c>
@@ -23895,7 +24354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>38744286</v>
       </c>
@@ -23927,7 +24386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>198009</v>
       </c>
@@ -23959,7 +24418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>143567</v>
       </c>
@@ -23991,7 +24450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>78954124</v>
       </c>
@@ -24023,7 +24482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>5082294</v>
       </c>
@@ -24053,7 +24512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>79130697</v>
       </c>
@@ -24083,7 +24542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>2295368</v>
       </c>
@@ -24115,7 +24574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>1003877</v>
       </c>
@@ -24147,7 +24606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>78990554</v>
       </c>
@@ -24179,7 +24638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>40566922</v>
       </c>
@@ -24209,7 +24668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>559761</v>
       </c>
@@ -24239,7 +24698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>3559600</v>
       </c>
@@ -24271,7 +24730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>519076</v>
       </c>
@@ -24301,7 +24760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>54458777</v>
       </c>
@@ -24331,7 +24790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>203088</v>
       </c>
@@ -24361,7 +24820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>79043363</v>
       </c>
@@ -24393,7 +24852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>78958543</v>
       </c>
@@ -24423,7 +24882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>140592</v>
       </c>
@@ -24455,7 +24914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>212742</v>
       </c>
@@ -24487,7 +24946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>22216798</v>
       </c>
@@ -24518,8 +24977,14 @@
       <c r="J342" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="343" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K342" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L342" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>562455</v>
       </c>
@@ -24551,7 +25016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>79046676</v>
       </c>
@@ -24583,7 +25048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>79329988</v>
       </c>
@@ -24615,7 +25080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>518072</v>
       </c>
@@ -24645,7 +25110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>79270831</v>
       </c>
@@ -24674,8 +25139,14 @@
       <c r="J347" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="348" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K347" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="L347" s="1" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>282741</v>
       </c>
@@ -24707,7 +25178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>825286</v>
       </c>
@@ -24738,8 +25209,14 @@
       <c r="J349" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="350" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K349" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L349" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>192396</v>
       </c>
@@ -24770,8 +25247,14 @@
       <c r="J350" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="351" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K350" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L350" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>79407061</v>
       </c>
@@ -24802,8 +25285,14 @@
       <c r="J351" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="352" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K351" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L351" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>79133402</v>
       </c>
@@ -24835,7 +25324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>79088485</v>
       </c>
@@ -24867,7 +25356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>3958322</v>
       </c>
@@ -24897,7 +25386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>79355018</v>
       </c>
@@ -24927,7 +25416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>194712</v>
       </c>
@@ -24959,7 +25448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>79012761</v>
       </c>
@@ -24988,8 +25477,14 @@
       <c r="J357" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="358" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K357" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L357" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>48324389</v>
       </c>
@@ -25021,7 +25516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>79200503</v>
       </c>
@@ -25052,8 +25547,14 @@
       <c r="J359" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="360" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K359" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L359" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>52912244</v>
       </c>
@@ -25083,7 +25584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>14960</v>
       </c>
@@ -25115,7 +25616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>79140903</v>
       </c>
@@ -25144,8 +25645,14 @@
       <c r="J362" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="363" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K362" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L362" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>857895</v>
       </c>
@@ -25177,7 +25684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>79012722</v>
       </c>
@@ -25208,8 +25715,14 @@
       <c r="J364" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="365" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K364" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L364" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>328767</v>
       </c>
@@ -25241,7 +25754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>12627202</v>
       </c>
@@ -25273,7 +25786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>25774395</v>
       </c>
@@ -25305,7 +25818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>43111221</v>
       </c>
@@ -25334,8 +25847,14 @@
       <c r="J368" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="369" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K368" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L368" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>573369</v>
       </c>
@@ -25366,8 +25885,14 @@
       <c r="J369" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="370" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K369" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L369" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>149368</v>
       </c>
@@ -25399,7 +25924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>464882</v>
       </c>
@@ -25429,7 +25954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>79038098</v>
       </c>
@@ -25461,7 +25986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>79000214</v>
       </c>
@@ -25491,7 +26016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>79452946</v>
       </c>
@@ -25523,7 +26048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>79127761</v>
       </c>
@@ -25553,7 +26078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>1162538</v>
       </c>
@@ -25584,8 +26109,14 @@
       <c r="J376" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="377" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K376" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L376" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>78974423</v>
       </c>
@@ -25614,8 +26145,14 @@
       <c r="J377" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="378" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K377" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L377" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>78998562</v>
       </c>
@@ -25645,7 +26182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>24720790</v>
       </c>
@@ -25676,8 +26213,14 @@
       <c r="J379" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="380" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K379" s="1" t="s">
+        <v>2152</v>
+      </c>
+      <c r="L379" s="1" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>1055676</v>
       </c>
@@ -25709,7 +26252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>79446925</v>
       </c>
@@ -25741,7 +26284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>79356797</v>
       </c>
@@ -25773,7 +26316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>136092</v>
       </c>
@@ -25805,7 +26348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>18114565</v>
       </c>
@@ -25836,8 +26379,14 @@
       <c r="J384" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="385" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K384" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L384" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>36274515</v>
       </c>
@@ -25866,8 +26415,14 @@
       <c r="J385" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="386" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K385" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L385" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>29524883</v>
       </c>
@@ -25897,7 +26452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>79106148</v>
       </c>
@@ -25929,7 +26484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>1045147</v>
       </c>
@@ -25961,7 +26516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>79161765</v>
       </c>
@@ -25991,7 +26546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>149629</v>
       </c>
@@ -26023,7 +26578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>16279578</v>
       </c>
@@ -26053,7 +26608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>383929</v>
       </c>
@@ -26083,7 +26638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>288709</v>
       </c>
@@ -26115,7 +26670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>79245967</v>
       </c>
@@ -26147,7 +26702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>1122662</v>
       </c>
@@ -26179,7 +26734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>264413</v>
       </c>
@@ -26209,7 +26764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>32223</v>
       </c>
@@ -26239,7 +26794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>79058795</v>
       </c>
@@ -26268,8 +26823,14 @@
       <c r="J398" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="399" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K398" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L398" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="399" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>259029</v>
       </c>
@@ -26301,7 +26862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>41537134</v>
       </c>
@@ -26332,8 +26893,14 @@
       <c r="J400" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="401" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K400" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L400" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="401" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>58686641</v>
       </c>
@@ -26365,7 +26932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>216262</v>
       </c>
@@ -26397,7 +26964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>79385451</v>
       </c>
@@ -26429,7 +26996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>279476</v>
       </c>
@@ -26459,7 +27026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>6996358</v>
       </c>
@@ -26489,7 +27056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>9484008</v>
       </c>
@@ -26519,7 +27086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>803426</v>
       </c>
@@ -26551,7 +27118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>212417</v>
       </c>
@@ -26583,7 +27150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>252426</v>
       </c>
@@ -26615,7 +27182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>217508</v>
       </c>
@@ -26647,7 +27214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>18739828</v>
       </c>
@@ -26679,7 +27246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>4650953</v>
       </c>
@@ -26710,8 +27277,14 @@
       <c r="J412" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="413" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K412" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L412" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>70814</v>
       </c>
@@ -26740,8 +27313,14 @@
       <c r="J413" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="414" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K413" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L413" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>912989</v>
       </c>
@@ -26771,7 +27350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>442773</v>
       </c>
@@ -26803,7 +27382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>70833</v>
       </c>
@@ -26835,7 +27414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>320055</v>
       </c>
@@ -26867,7 +27446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>261727</v>
       </c>
@@ -26898,8 +27477,14 @@
       <c r="J418" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="419" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K418" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L418" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>30087221</v>
       </c>
@@ -26929,7 +27514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>37081</v>
       </c>
@@ -26959,7 +27544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>79096549</v>
       </c>
@@ -26988,8 +27573,14 @@
       <c r="J421" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="422" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K421" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L421" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>16799238</v>
       </c>
@@ -27018,8 +27609,14 @@
       <c r="J422" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="423" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K422" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L422" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>948595</v>
       </c>
@@ -27048,8 +27645,14 @@
       <c r="J423" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="424" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K423" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L423" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>38329857</v>
       </c>
@@ -27079,7 +27682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>479946</v>
       </c>
@@ -27111,7 +27714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>44475689</v>
       </c>
@@ -27143,7 +27746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>855132</v>
       </c>
@@ -27175,7 +27778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>710713</v>
       </c>
@@ -27207,7 +27810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>79322268</v>
       </c>
@@ -27239,7 +27842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>79375576</v>
       </c>
@@ -27271,7 +27874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>183149</v>
       </c>
@@ -27301,7 +27904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>15839</v>
       </c>
@@ -27332,8 +27935,14 @@
       <c r="J432" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="433" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K432" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L432" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="433" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>16054</v>
       </c>
@@ -27364,8 +27973,14 @@
       <c r="J433" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="434" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K433" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L433" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>32148</v>
       </c>
@@ -27395,7 +28010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>54997</v>
       </c>
@@ -27426,8 +28041,14 @@
       <c r="J435" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="436" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K435" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L435" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="436" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>62888</v>
       </c>
@@ -27459,7 +28080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>80503</v>
       </c>
@@ -27491,7 +28112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>84987</v>
       </c>
@@ -27522,8 +28143,14 @@
       <c r="J438" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="439" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K438" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L438" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="439" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>100307</v>
       </c>
@@ -27555,7 +28182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>101447</v>
       </c>
@@ -27586,8 +28213,14 @@
       <c r="J440" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="441" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K440" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L440" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="441" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>104881</v>
       </c>
@@ -27619,7 +28252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>129522</v>
       </c>
@@ -27650,8 +28283,14 @@
       <c r="J442" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="443" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K442" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L442" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="443" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>138260</v>
       </c>
@@ -27683,7 +28322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>156685</v>
       </c>
@@ -27714,8 +28353,14 @@
       <c r="J444" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="445" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K444" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L444" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="445" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>165728</v>
       </c>
@@ -27746,8 +28391,14 @@
       <c r="J445" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="446" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K445" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L445" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="446" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>166052</v>
       </c>
@@ -27778,8 +28429,14 @@
       <c r="J446" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="447" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K446" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L446" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="447" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>223068</v>
       </c>
@@ -27811,7 +28468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>229157</v>
       </c>
@@ -27843,7 +28500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>239107</v>
       </c>
@@ -27875,7 +28532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>241189</v>
       </c>
@@ -27907,7 +28564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>247160</v>
       </c>
@@ -27939,7 +28596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>283994</v>
       </c>
@@ -27968,8 +28625,14 @@
       <c r="J452" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="453" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K452" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L452" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="453" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>323058</v>
       </c>
@@ -27999,7 +28662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>333166</v>
       </c>
@@ -28031,7 +28694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>359634</v>
       </c>
@@ -28063,7 +28726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>434731</v>
       </c>
@@ -28095,7 +28758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>437563</v>
       </c>
@@ -28125,7 +28788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>468798</v>
       </c>
@@ -28157,7 +28820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>476674</v>
       </c>
@@ -28188,8 +28851,14 @@
       <c r="J459" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="460" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K459" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L459" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="460" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>502388</v>
       </c>
@@ -28220,8 +28889,14 @@
       <c r="J460" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="461" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K460" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L460" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="461" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>550552</v>
       </c>
@@ -28252,8 +28927,14 @@
       <c r="J461" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="462" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K461" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L461" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="462" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>575486</v>
       </c>
@@ -28285,7 +28966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>651735</v>
       </c>
@@ -28316,8 +28997,14 @@
       <c r="J463" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="464" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K463" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L463" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="464" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>683642</v>
       </c>
@@ -28349,7 +29036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>1019572</v>
       </c>
@@ -28381,7 +29068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>1207461</v>
       </c>
@@ -28413,7 +29100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>1260813</v>
       </c>
@@ -28444,8 +29131,14 @@
       <c r="J467" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="468" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K467" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L467" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="468" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>1290376</v>
       </c>
@@ -28477,7 +29170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>1323426</v>
       </c>
@@ -28507,7 +29200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>1326002</v>
       </c>
@@ -28536,8 +29229,14 @@
       <c r="J470" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="471" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K470" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L470" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="471" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>1592581</v>
       </c>
@@ -28566,8 +29265,14 @@
       <c r="J471" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="472" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K471" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L471" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="472" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>1713101</v>
       </c>
@@ -28599,7 +29304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>1748651</v>
       </c>
@@ -28631,7 +29336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>2277363</v>
       </c>
@@ -28661,7 +29366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>3148376</v>
       </c>
@@ -28693,7 +29398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>3289606</v>
       </c>
@@ -28723,7 +29428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>3627815</v>
       </c>
@@ -28755,7 +29460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>3940137</v>
       </c>
@@ -28784,8 +29489,14 @@
       <c r="J478" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="479" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="K478" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L478" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="479" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>4528110</v>
       </c>
@@ -28815,7 +29526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>4765242</v>
       </c>
@@ -28847,7 +29558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>4935945</v>
       </c>
@@ -28879,7 +29590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>5214587</v>
       </c>
@@ -28909,7 +29620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>5898031</v>
       </c>
@@ -28940,8 +29651,14 @@
       <c r="J483" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="484" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K483" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L483" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="484" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>6718435</v>
       </c>
@@ -28972,8 +29689,14 @@
       <c r="J484" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="485" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K484" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L484" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="485" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>6767329</v>
       </c>
@@ -29005,7 +29728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>7816439</v>
       </c>
@@ -29037,7 +29760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>8272643</v>
       </c>
@@ -29069,7 +29792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>8294654</v>
       </c>
@@ -29101,7 +29824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>8637972</v>
       </c>
@@ -29133,7 +29856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>8702435</v>
       </c>
@@ -29164,8 +29887,14 @@
       <c r="J490" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="491" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K490" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L490" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="491" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>10202789</v>
       </c>
@@ -29197,7 +29926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>11427183</v>
       </c>
@@ -29229,7 +29958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>11664675</v>
       </c>
@@ -29261,7 +29990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>12453584</v>
       </c>
@@ -29293,7 +30022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>13827087</v>
       </c>
@@ -29325,7 +30054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>15345969</v>
       </c>
@@ -29357,7 +30086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>15618520</v>
       </c>
@@ -29389,7 +30118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>16878364</v>
       </c>
@@ -29421,7 +30150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>17142719</v>
       </c>
@@ -29453,7 +30182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>17743548</v>
       </c>
@@ -29485,7 +30214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>18393879</v>
       </c>
@@ -29517,7 +30246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>19801806</v>
       </c>
@@ -29549,7 +30278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>21285575</v>
       </c>
@@ -29581,7 +30310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>22284921</v>
       </c>
@@ -29612,8 +30341,14 @@
       <c r="J504" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="505" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K504" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L504" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="505" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>23978968</v>
       </c>
@@ -29644,8 +30379,14 @@
       <c r="J505" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="506" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K505" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L505" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="506" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>24176022</v>
       </c>
@@ -29677,7 +30418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>24903067</v>
       </c>
@@ -29709,7 +30450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>27844237</v>
       </c>
@@ -29741,7 +30482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>28052583</v>
       </c>
@@ -29773,7 +30514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>31360218</v>
       </c>
@@ -29805,7 +30546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>31885295</v>
       </c>
@@ -29837,7 +30578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>35904211</v>
       </c>
@@ -29869,7 +30610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>36158079</v>
       </c>
@@ -29901,7 +30642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>37961120</v>
       </c>
@@ -29931,7 +30672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>41096943</v>
       </c>
@@ -29963,7 +30704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>42642326</v>
       </c>
@@ -29995,7 +30736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>42690573</v>
       </c>
@@ -30026,8 +30767,14 @@
       <c r="J517" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="518" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K517" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L517" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="518" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>44072944</v>
       </c>
@@ -30059,7 +30806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>45808255</v>
       </c>
@@ -30091,7 +30838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>46011113</v>
       </c>
@@ -30121,7 +30868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>47865626</v>
       </c>
@@ -30152,8 +30899,14 @@
       <c r="J521" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="522" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K521" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L521" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="522" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>56136591</v>
       </c>
@@ -30185,7 +30938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>58302703</v>
       </c>
@@ -30217,7 +30970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>59385935</v>
       </c>
@@ -30249,7 +31002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>60018731</v>
       </c>
@@ -30279,7 +31032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>65266270</v>
       </c>
@@ -30311,7 +31064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>69527217</v>
       </c>
@@ -30342,8 +31095,14 @@
       <c r="J527" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="528" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K527" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L527" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="528" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>1040272</v>
       </c>
@@ -30375,7 +31134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>24852544</v>
       </c>
@@ -30407,7 +31166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>111303</v>
       </c>
@@ -30438,8 +31197,14 @@
       <c r="J530" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="531" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K530" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L530" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="531" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>79243674</v>
       </c>
@@ -30471,7 +31236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>19222468</v>
       </c>
@@ -30503,7 +31268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>1059601</v>
       </c>
@@ -30533,7 +31298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>407305</v>
       </c>
@@ -30563,7 +31328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>1984346</v>
       </c>
@@ -30594,8 +31359,14 @@
       <c r="J535" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="536" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K535" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L535" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="536" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>16877439</v>
       </c>
@@ -30627,7 +31398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>13641613</v>
       </c>
@@ -30656,8 +31427,14 @@
       <c r="J537" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="538" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K537" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L537" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="538" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>289358</v>
       </c>
@@ -30689,7 +31466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>119586</v>
       </c>
@@ -30721,7 +31498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>267735</v>
       </c>
@@ -30753,7 +31530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>1260846</v>
       </c>
@@ -30784,8 +31561,14 @@
       <c r="J541" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="542" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K541" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L541" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="542" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>522569</v>
       </c>
@@ -30816,8 +31599,14 @@
       <c r="J542" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="543" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K542" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L542" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="543" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>8347192</v>
       </c>
@@ -30849,7 +31638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>28663910</v>
       </c>
@@ -30880,8 +31669,14 @@
       <c r="J544" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="545" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K544" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L544" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="545" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>1996540</v>
       </c>
@@ -30913,7 +31708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>17973255</v>
       </c>
@@ -30943,7 +31738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>1448476</v>
       </c>
@@ -30975,7 +31770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>20457284</v>
       </c>
@@ -31006,8 +31801,14 @@
       <c r="J548" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="549" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K548" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L548" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="549" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>943004</v>
       </c>
@@ -31039,7 +31840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>47808351</v>
       </c>
@@ -31069,7 +31870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>5434936</v>
       </c>
@@ -31101,7 +31902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>20309470</v>
       </c>
@@ -31132,8 +31933,14 @@
       <c r="J552" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="553" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K552" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L552" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="553" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>321686</v>
       </c>
@@ -31164,8 +31971,14 @@
       <c r="J553" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="554" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K553" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L553" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="554" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>38770040</v>
       </c>
@@ -31194,8 +32007,14 @@
       <c r="J554" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="555" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K554" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L554" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="555" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>79423263</v>
       </c>
@@ -31227,7 +32046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>395236</v>
       </c>
@@ -31259,7 +32078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>290440</v>
       </c>
@@ -31291,7 +32110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>343643</v>
       </c>
@@ -31323,7 +32142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>142601</v>
       </c>
@@ -31354,8 +32173,14 @@
       <c r="J559" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="560" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K559" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L559" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="560" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>530289</v>
       </c>
@@ -31387,7 +32212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>19603918</v>
       </c>
@@ -31419,7 +32244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>14541175</v>
       </c>
@@ -31450,8 +32275,14 @@
       <c r="J562" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="563" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K562" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L562" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="563" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>9157277</v>
       </c>
@@ -31483,7 +32314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>11158224</v>
       </c>
@@ -31514,8 +32345,14 @@
       <c r="J564" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="565" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K564" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L564" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="565" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>12213723</v>
       </c>
@@ -31546,8 +32383,14 @@
       <c r="J565" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="566" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K565" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L565" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="566" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>1120068</v>
       </c>
@@ -31579,7 +32422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>13441</v>
       </c>
@@ -31610,8 +32453,14 @@
       <c r="J567" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="568" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K567" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L567" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="568" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>258664</v>
       </c>
@@ -31642,8 +32491,14 @@
       <c r="J568" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="569" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K568" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L568" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="569" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>7585619</v>
       </c>
@@ -31675,7 +32530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>2030142</v>
       </c>
@@ -31706,8 +32561,14 @@
       <c r="J570" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="571" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K570" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L570" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="571" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>28840457</v>
       </c>
@@ -31737,7 +32598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>612208</v>
       </c>
@@ -31769,7 +32630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>109389</v>
       </c>
@@ -31801,7 +32662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>79331292</v>
       </c>
@@ -31833,7 +32694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>526780</v>
       </c>
@@ -31865,7 +32726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>79505314</v>
       </c>
@@ -31897,7 +32758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>47826</v>
       </c>
@@ -31928,8 +32789,14 @@
       <c r="J577" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="578" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K577" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L577" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="578" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>23482284</v>
       </c>
@@ -31960,8 +32827,14 @@
       <c r="J578" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="579" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K578" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L578" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="579" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>33569857</v>
       </c>
@@ -31993,7 +32866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>16896091</v>
       </c>
@@ -32023,7 +32896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>587153</v>
       </c>
@@ -32055,7 +32928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>4499172</v>
       </c>
@@ -32084,8 +32957,14 @@
       <c r="J582" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="583" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K582" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L582" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="583" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>144535</v>
       </c>
@@ -32117,7 +32996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>7247542</v>
       </c>
@@ -32149,7 +33028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>40662156</v>
       </c>
@@ -32180,8 +33059,14 @@
       <c r="J585" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="586" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K585" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L585" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="586" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>23660030</v>
       </c>
@@ -32213,7 +33098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>163543</v>
       </c>
@@ -32245,7 +33130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>80467</v>
       </c>
@@ -32275,7 +33160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>56136591</v>
       </c>
@@ -32307,7 +33192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>2492093</v>
       </c>
@@ -32339,7 +33224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>17784974</v>
       </c>
@@ -32371,7 +33256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
         <v>8391452</v>
       </c>
@@ -32403,7 +33288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>20968427</v>
       </c>
@@ -32435,7 +33320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>256236</v>
       </c>
@@ -32465,7 +33350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>51996934</v>
       </c>
@@ -32497,7 +33382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>13148611</v>
       </c>
@@ -32529,7 +33414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>40984270</v>
       </c>
@@ -32559,7 +33444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>3781960</v>
       </c>
@@ -32591,7 +33476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>8866125</v>
       </c>
@@ -32623,7 +33508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>71683</v>
       </c>
@@ -32654,8 +33539,14 @@
       <c r="J600" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="601" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K600" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L600" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="601" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>23116937</v>
       </c>
@@ -32685,7 +33576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>47095907</v>
       </c>
@@ -32716,8 +33607,14 @@
       <c r="J602" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="603" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K602" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L602" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="603" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>212629</v>
       </c>
@@ -32748,8 +33645,14 @@
       <c r="J603" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="604" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K603" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L603" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="604" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>39404</v>
       </c>
@@ -32781,7 +33684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>40449862</v>
       </c>
@@ -32813,7 +33716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:10" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:12" ht="374.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>475886</v>
       </c>
@@ -32844,8 +33747,14 @@
       <c r="J606" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="607" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K606" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L606" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="607" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>272595</v>
       </c>
@@ -32877,7 +33786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>415956</v>
       </c>
@@ -32909,7 +33818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="1">
         <v>10112665</v>
       </c>
@@ -32940,8 +33849,14 @@
       <c r="J609" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="610" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K609" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L609" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="610" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="1">
         <v>27385986</v>
       </c>
@@ -32972,8 +33887,14 @@
       <c r="J610" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="611" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K610" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L610" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="611" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>8719100</v>
       </c>
@@ -33002,8 +33923,14 @@
       <c r="J611" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="612" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K611" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L611" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="612" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>36644714</v>
       </c>
@@ -33034,8 +33961,14 @@
       <c r="J612" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="613" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K612" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L612" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="613" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>25851972</v>
       </c>
@@ -33067,7 +34000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>4617069</v>
       </c>
@@ -33099,7 +34032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>65255334</v>
       </c>
@@ -33131,7 +34064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>533077</v>
       </c>
@@ -33163,7 +34096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="1">
         <v>4907053</v>
       </c>
@@ -33195,7 +34128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>18343661</v>
       </c>
@@ -33227,7 +34160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>388716</v>
       </c>
@@ -33257,7 +34190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>79088432</v>
       </c>
@@ -33289,7 +34222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="1">
         <v>15934081</v>
       </c>
@@ -33321,7 +34254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>484255</v>
       </c>
@@ -33352,8 +34285,14 @@
       <c r="J622" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="623" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K622" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L622" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="623" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>65124</v>
       </c>
@@ -33385,7 +34324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>17796231</v>
       </c>
@@ -33417,7 +34356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>446671</v>
       </c>
@@ -33447,7 +34386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>14087705</v>
       </c>
@@ -33478,8 +34417,14 @@
       <c r="J626" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="627" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K626" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L626" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="627" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>365533</v>
       </c>
@@ -33509,7 +34454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>4734439</v>
       </c>
@@ -33541,7 +34486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>13929101</v>
       </c>
@@ -33571,7 +34516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>209771</v>
       </c>
@@ -33602,8 +34547,14 @@
       <c r="J630" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="631" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K630" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L630" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="631" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>79219962</v>
       </c>
@@ -33635,7 +34586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="1">
         <v>1919055</v>
       </c>
@@ -33666,8 +34617,14 @@
       <c r="J632" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="633" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K632" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L632" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="633" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="1">
         <v>77077</v>
       </c>
@@ -33699,7 +34656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="1">
         <v>184143</v>
       </c>
@@ -33730,8 +34687,14 @@
       <c r="J634" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="635" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K634" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L634" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="635" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="1">
         <v>409795</v>
       </c>
@@ -33763,7 +34726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="1">
         <v>3277511</v>
       </c>
@@ -33794,8 +34757,14 @@
       <c r="J636" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="637" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K636" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L636" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="637" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>579616</v>
       </c>
@@ -33825,7 +34794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:12" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>512220</v>
       </c>
@@ -33855,7 +34824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>837779</v>
       </c>
@@ -33885,7 +34854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>331795</v>
       </c>
@@ -33917,7 +34886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>2676904</v>
       </c>
@@ -33949,7 +34918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>979344</v>
       </c>
@@ -33981,7 +34950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>79396682</v>
       </c>
@@ -34011,7 +34980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>151014</v>
       </c>
@@ -34043,7 +35012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="1">
         <v>1073582</v>
       </c>
@@ -34074,8 +35043,14 @@
       <c r="J645" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="646" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K645" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L645" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="646" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="1">
         <v>9031848</v>
       </c>
@@ -34106,8 +35081,14 @@
       <c r="J646" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="647" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K646" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L646" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="647" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="1">
         <v>12615192</v>
       </c>
@@ -34139,7 +35120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="1">
         <v>10287</v>
       </c>
@@ -34171,7 +35152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="1">
         <v>42340744</v>
       </c>
@@ -34203,7 +35184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>34186</v>
       </c>
@@ -34235,7 +35216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>1263436</v>
       </c>
@@ -34265,7 +35246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:10" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:12" ht="302.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="1">
         <v>386903</v>
       </c>
@@ -34297,7 +35278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="1">
         <v>1398059</v>
       </c>
@@ -34329,7 +35310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="1">
         <v>14407505</v>
       </c>
@@ -34358,8 +35339,14 @@
       <c r="J654" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="655" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K654" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L654" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="655" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="1">
         <v>79405601</v>
       </c>
@@ -34389,7 +35376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="1">
         <v>1547163</v>
       </c>
@@ -34420,8 +35407,14 @@
       <c r="J656" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="657" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K656" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L656" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="657" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="1">
         <v>9457864</v>
       </c>
@@ -34453,7 +35446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="1">
         <v>10035974</v>
       </c>
@@ -34483,7 +35476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="1">
         <v>78940799</v>
       </c>
@@ -34515,7 +35508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="1">
         <v>11016430</v>
       </c>
@@ -34547,7 +35540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:10" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:12" ht="403.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="1">
         <v>20776444</v>
       </c>
@@ -34578,8 +35571,14 @@
       <c r="J661" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="662" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K661" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L661" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="662" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="1">
         <v>14225664</v>
       </c>
@@ -34611,7 +35610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>79521584</v>
       </c>
@@ -34641,7 +35640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>24352671</v>
       </c>
@@ -34673,7 +35672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>325615</v>
       </c>
@@ -34703,7 +35702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:10" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:12" ht="388.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>773472</v>
       </c>
@@ -34735,7 +35734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="1">
         <v>38569536</v>
       </c>
@@ -34767,7 +35766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>4580120</v>
       </c>
@@ -34796,8 +35795,14 @@
       <c r="J668" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="669" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K668" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="L668" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="669" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>437627</v>
       </c>
@@ -34829,7 +35834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="1">
         <v>10207</v>
       </c>
@@ -34859,7 +35864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="1">
         <v>29934</v>
       </c>
@@ -34889,7 +35894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="1">
         <v>51071</v>
       </c>
@@ -34920,8 +35925,14 @@
       <c r="J672" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="673" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K672" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L672" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="673" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="1">
         <v>52062</v>
       </c>
@@ -34952,8 +35963,14 @@
       <c r="J673" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="674" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K673" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L673" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="674" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="1">
         <v>70030</v>
       </c>
@@ -34984,8 +36001,14 @@
       <c r="J674" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="675" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K674" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L674" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="675" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="1">
         <v>96651</v>
       </c>
@@ -35015,7 +36038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="1">
         <v>102511</v>
       </c>
@@ -35047,7 +36070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="1">
         <v>114589</v>
       </c>
@@ -35079,7 +36102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>126110</v>
       </c>
@@ -35110,8 +36133,14 @@
       <c r="J678" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="679" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K678" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L678" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="679" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>142266</v>
       </c>
@@ -35143,7 +36172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="1">
         <v>144184</v>
       </c>
@@ -35173,7 +36202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="1">
         <v>147950</v>
       </c>
@@ -35202,8 +36231,14 @@
       <c r="J681" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="682" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K681" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L681" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="682" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="1">
         <v>158672</v>
       </c>
@@ -35235,7 +36270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="1">
         <v>169568</v>
       </c>
@@ -35267,7 +36302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="1">
         <v>180217</v>
       </c>
@@ -35297,7 +36332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A685" s="1">
         <v>182091</v>
       </c>
@@ -35328,8 +36363,14 @@
       <c r="J685" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="686" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K685" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L685" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="686" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="1">
         <v>190373</v>
       </c>
@@ -35359,7 +36400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="1">
         <v>191104</v>
       </c>
@@ -35391,7 +36432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="1">
         <v>191152</v>
       </c>
@@ -35422,8 +36463,14 @@
       <c r="J688" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="689" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K688" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L688" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="689" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="1">
         <v>237724</v>
       </c>
@@ -35455,7 +36502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="1">
         <v>258697</v>
       </c>
@@ -35487,7 +36534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="1">
         <v>268332</v>
       </c>
@@ -35517,7 +36564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="1">
         <v>279385</v>
       </c>
@@ -35547,7 +36594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>280517</v>
       </c>
@@ -35579,7 +36626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>315595</v>
       </c>
@@ -35608,8 +36655,14 @@
       <c r="J694" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="695" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K694" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="L694" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="695" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="1">
         <v>341050</v>
       </c>
@@ -35639,7 +36692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A696" s="1">
         <v>361670</v>
       </c>
@@ -35671,7 +36724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="1">
         <v>414090</v>
       </c>
@@ -35703,7 +36756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A698" s="1">
         <v>421383</v>
       </c>
@@ -35733,7 +36786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:10" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:12" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A699" s="1">
         <v>427370</v>
       </c>
@@ -35765,7 +36818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>428714</v>
       </c>
@@ -35796,8 +36849,14 @@
       <c r="J700" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="701" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K700" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L700" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="701" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>453034</v>
       </c>
@@ -35829,7 +36888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A702" s="1">
         <v>511029</v>
       </c>
@@ -35861,7 +36920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:10" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:12" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A703" s="1">
         <v>516329</v>
       </c>
@@ -35893,7 +36952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A704" s="1">
         <v>530468</v>
       </c>
@@ -35922,8 +36981,14 @@
       <c r="J704" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="705" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K704" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="L704" s="1" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="705" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="1">
         <v>557405</v>
       </c>
@@ -35955,7 +37020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A706" s="1">
         <v>574814</v>
       </c>
@@ -35984,8 +37049,14 @@
       <c r="J706" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="707" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K706" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L706" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="707" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>630739</v>
       </c>
@@ -36015,7 +37086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>666228</v>
       </c>
@@ -36047,7 +37118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A709" s="1">
         <v>697762</v>
       </c>
@@ -36077,7 +37148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A710" s="1">
         <v>749374</v>
       </c>
@@ -36108,8 +37179,14 @@
       <c r="J710" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="711" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K710" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L710" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="711" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A711" s="1">
         <v>820636</v>
       </c>
@@ -36139,7 +37216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A712" s="1">
         <v>895095</v>
       </c>
@@ -36169,7 +37246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A713" s="1">
         <v>934502</v>
       </c>
@@ -36201,7 +37278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A714" s="1">
         <v>953381</v>
       </c>
@@ -36231,7 +37308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A715" s="1">
         <v>957829</v>
       </c>
@@ -36263,7 +37340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
         <v>1095174</v>
       </c>
@@ -36295,7 +37372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:10" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:12" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>1174325</v>
       </c>
@@ -36327,7 +37404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>3877312</v>
       </c>
@@ -36359,7 +37436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A719" s="1">
         <v>19008548</v>
       </c>
@@ -36390,8 +37467,14 @@
       <c r="J719" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="720" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K719" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="L719" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="720" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A720" s="1">
         <v>79181756</v>
       </c>
@@ -36423,7 +37506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A721" s="1">
         <v>606628</v>
       </c>
@@ -36455,7 +37538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A722" s="1">
         <v>79155092</v>
       </c>
@@ -36485,7 +37568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A723" s="1">
         <v>79070940</v>
       </c>
@@ -36517,7 +37600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>321276</v>
       </c>
@@ -36549,7 +37632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>144184</v>
       </c>
@@ -36579,7 +37662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>289724</v>
       </c>
@@ -36611,7 +37694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:10" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:12" ht="316.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A727" s="1">
         <v>282491</v>
       </c>
@@ -36642,8 +37725,14 @@
       <c r="J727" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="728" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K727" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L727" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="728" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A728" s="1">
         <v>79190939</v>
       </c>
@@ -36673,7 +37762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:10" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:12" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A729" s="1">
         <v>79411731</v>
       </c>
@@ -36704,8 +37793,14 @@
       <c r="J729" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="730" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K729" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L729" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="730" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A730" s="1">
         <v>239238</v>
       </c>
@@ -36736,8 +37831,14 @@
       <c r="J730" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="731" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K730" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L730" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="731" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A731" s="1">
         <v>79125543</v>
       </c>
@@ -36769,7 +37870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:10" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:12" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A732" s="1">
         <v>79376076</v>
       </c>
@@ -36798,8 +37899,14 @@
       <c r="J732" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="733" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K732" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L732" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="733" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A733" s="1">
         <v>79010054</v>
       </c>
@@ -36828,8 +37935,14 @@
       <c r="J733" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="734" spans="1:10" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K733" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L733" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="734" spans="1:12" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A734" s="1">
         <v>282015</v>
       </c>
@@ -36859,7 +37972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>79354571</v>
       </c>
@@ -36889,7 +38002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>935185</v>
       </c>
@@ -36918,8 +38031,14 @@
       <c r="J736" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="737" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K736" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="L736" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="737" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>377051</v>
       </c>
@@ -36949,7 +38068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:10" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:12" ht="331.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>1000981</v>
       </c>
@@ -36981,7 +38100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:10" ht="360" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:12" ht="360" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A739" s="1">
         <v>336343</v>
       </c>
@@ -37013,7 +38132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
         <v>79334448</v>
       </c>
@@ -37045,7 +38164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>79280524</v>
       </c>
@@ -37075,7 +38194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>86309</v>
       </c>
@@ -37107,7 +38226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A743" s="1">
         <v>434705</v>
       </c>
@@ -37139,7 +38258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:10" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A744" s="1">
         <v>1000598</v>
       </c>
@@ -37169,7 +38288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>79275052</v>
       </c>
@@ -37199,7 +38318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>424985</v>
       </c>
@@ -37230,8 +38349,14 @@
       <c r="J746" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="747" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K746" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L746" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="747" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A747" s="1">
         <v>79396019</v>
       </c>
@@ -37262,8 +38387,14 @@
       <c r="J747" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="748" spans="1:10" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K747" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L747" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="748" spans="1:12" ht="345.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A748" s="1">
         <v>79343060</v>
       </c>
@@ -37293,7 +38424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:10" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:12" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A749" s="1">
         <v>1112290</v>
       </c>
@@ -37323,7 +38454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A750" s="1">
         <v>79477227</v>
       </c>
@@ -37355,7 +38486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A751" s="1">
         <v>79022776</v>
       </c>
@@ -37387,7 +38518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A752" s="1">
         <v>9160112</v>
       </c>
@@ -37419,7 +38550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A753" s="1">
         <v>79093901</v>
       </c>
@@ -37449,7 +38580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A754" s="1">
         <v>464179</v>
       </c>
@@ -37479,7 +38610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A755" s="1">
         <v>56051</v>
       </c>
@@ -37511,7 +38642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>32711</v>
       </c>
@@ -37542,8 +38673,14 @@
       <c r="J756" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="757" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K756" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L756" s="1" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="757" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>4344735</v>
       </c>
@@ -37575,7 +38712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:12" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A758" s="1">
         <v>16544933</v>
       </c>
@@ -37605,7 +38742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A759" s="1">
         <v>1159535</v>
       </c>
@@ -37636,8 +38773,14 @@
       <c r="J759" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="760" spans="1:10" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K759" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L759" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="760" spans="1:12" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A760" s="1">
         <v>8803076</v>
       </c>
@@ -37667,7 +38810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:10" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:12" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A761" s="1">
         <v>196873</v>
       </c>
@@ -37699,7 +38842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>79487730</v>
       </c>
@@ -37729,7 +38872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>1282568</v>
       </c>
@@ -37761,7 +38904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A764" s="1">
         <v>79050172</v>
       </c>
@@ -37791,7 +38934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A765" s="1">
         <v>282144</v>
       </c>
@@ -37821,7 +38964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A766" s="1">
         <v>179442</v>
       </c>
@@ -37853,7 +38996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A767" s="1">
         <v>1302860</v>
       </c>
@@ -37883,7 +39026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="768" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A768" s="1">
         <v>79065371</v>
       </c>
@@ -37913,6 +39056,12 @@
       </c>
       <c r="J768" s="1">
         <v>0</v>
+      </c>
+      <c r="K768" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="L768" s="1" t="s">
+        <v>2135</v>
       </c>
     </row>
     <row r="769" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -38411,7 +39560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:10" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:12" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>79292266</v>
       </c>
@@ -38441,7 +39590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:12" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A786" s="1">
         <v>253906</v>
       </c>
@@ -38472,8 +39621,14 @@
       <c r="J786" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="787" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K786" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="L786" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="787" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A787" s="1">
         <v>79249064</v>
       </c>
@@ -38503,7 +39658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="788" spans="1:10" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:12" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
         <v>529656</v>
       </c>
@@ -38533,7 +39688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="789" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A789" s="1">
         <v>225120</v>
       </c>
@@ -38565,7 +39720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="790" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A790" s="1">
         <v>79274383</v>
       </c>
@@ -38595,7 +39750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="791" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A791" s="1">
         <v>79496006</v>
       </c>
